--- a/design/copy/文案对照.xlsx
+++ b/design/copy/文案对照.xlsx
@@ -448,42 +448,42 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>网站全部文案（中英对照），由 scripts/export-copy.mjs 从语言包 src/locales/zh.json、en.json 导出，按页面阅读顺序排列。</t>
+          <t>网站全部文案（中英对照），从语言包 src/locales/zh.json、en.json 导出，按页面阅读顺序排列。</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>在「修改后中文」「修改后英文」两列填写新文案；不需要改的留空即可。</t>
+          <t>在「修改后中文」「修改后英文」两列填写新文案；不需要改的留空即可。填好后运行 npm run copy:import 写回语言包。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>「备注」可写想法，比如「删掉」「合并到上一条」「语气更口语」。</t>
+          <t>「备注」可写想法，比如「删掉」「合并到上一条」「语气更口语」；备注不会自动生效，导入时会列出来。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>「键名」就是语言包里的键，由页面位置组成：项目 id、章节 id、模块序号、图片 id 等。改文案时直接改两个 JSON 文件里对应键的值即可。</t>
+          <t>「键名」就是语言包里的键，由页面位置组成：项目 id、章节 id、模块序号、图片 id 等。请不要改键名和「中文（当前）」「English (current)」两列，导入靠它们核对。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>最后一列「代码路径」是回写时用的定位，请不要改。</t>
+          <t>带 {n}、{date} 这类花括号的是占位符，会替换成数字或日期，修改时请保留。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>「嵌入页面」是 public/embeds 下独立的可交互演示页，文字还写在各自的 HTML 里（data-zh 属性），不在语言包中，按文件行号定位。</t>
+          <t>「嵌入页面」是 public/embeds 下独立的可交互演示页，文字写在各自的 HTML 里，不在语言包中；这一页的修改导入时只会列出，需要手动改。</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>全站界面：150</t>
+          <t>全站界面：153</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gocus：35</t>
+          <t>Gocus：36</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>合计：1170</t>
+          <t>合计：1174</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1643,6 +1643,34 @@
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
       <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>src/locales/*.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>studies.gocus.identity.navLabel</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>图标</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>src/locales/*.json</t>
         </is>
@@ -7304,7 +7332,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:51</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -7322,7 +7350,7 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:51</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7360,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:52</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -7350,7 +7378,7 @@
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:52</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7388,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:57</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -7378,7 +7406,7 @@
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:57</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7388,7 +7416,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:58</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -7406,7 +7434,7 @@
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:58</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7444,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:60</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -7434,7 +7462,7 @@
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:60</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7472,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:61</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -7462,7 +7490,7 @@
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:61</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7500,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:62</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -7490,7 +7518,7 @@
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:62</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7500,7 +7528,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:63</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -7518,7 +7546,7 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:63</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7556,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:68</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -7546,7 +7574,7 @@
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:68</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7584,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:69</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7574,7 +7602,7 @@
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:69</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7584,7 +7612,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:71</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -7602,7 +7630,7 @@
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:71</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7612,7 +7640,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:72</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -7630,7 +7658,7 @@
       <c r="G13" s="2" t="n"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:72</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7668,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:78</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -7658,7 +7686,7 @@
       <c r="G14" s="2" t="n"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:78</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7668,7 +7696,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:79</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -7686,7 +7714,7 @@
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:79</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7696,7 +7724,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:81</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -7714,7 +7742,7 @@
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:81</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7752,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:82</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -7742,7 +7770,7 @@
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:82</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7752,7 +7780,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:84</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -7770,7 +7798,7 @@
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:84</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7808,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:85</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -7798,7 +7826,7 @@
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:85</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7836,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:87</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -7826,7 +7854,7 @@
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:87</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7864,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:88</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -7854,7 +7882,7 @@
       <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:88</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7892,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:90</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -7882,7 +7910,7 @@
       <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:90</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7920,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html</t>
+          <t>public/embeds/gocus/code/index.html:91</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -7910,7 +7938,7 @@
       <c r="G23" s="2" t="n"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/code/index.html:91</t>
+          <t>public/embeds/gocus/code/index.html</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7948,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:128</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -7938,7 +7966,7 @@
       <c r="G24" s="2" t="n"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:128</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7976,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:129</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -7966,7 +7994,7 @@
       <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:129</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -7976,7 +8004,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:130</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -7994,7 +8022,7 @@
       <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:130</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -8004,7 +8032,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:133</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -8022,7 +8050,7 @@
       <c r="G27" s="2" t="n"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:133</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -8032,7 +8060,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:133</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -8050,7 +8078,7 @@
       <c r="G28" s="2" t="n"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:133</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -8060,7 +8088,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:134</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -8078,7 +8106,7 @@
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:134</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -8088,7 +8116,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:134</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -8106,7 +8134,7 @@
       <c r="G30" s="2" t="n"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:134</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -8116,7 +8144,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:135</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -8134,7 +8162,7 @@
       <c r="G31" s="2" t="n"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:135</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -8144,7 +8172,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:135</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -8162,7 +8190,7 @@
       <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:135</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8200,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:136</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -8190,7 +8218,7 @@
       <c r="G33" s="2" t="n"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:136</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8228,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:136</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -8218,7 +8246,7 @@
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:136</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -8228,7 +8256,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:137</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -8246,7 +8274,7 @@
       <c r="G35" s="2" t="n"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:137</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8284,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:137</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -8274,7 +8302,7 @@
       <c r="G36" s="2" t="n"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:137</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8312,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:144</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -8302,7 +8330,7 @@
       <c r="G37" s="2" t="n"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:144</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -8312,7 +8340,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:145</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -8330,7 +8358,7 @@
       <c r="G38" s="2" t="n"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:145</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -8340,7 +8368,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:150</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -8358,7 +8386,7 @@
       <c r="G39" s="2" t="n"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:150</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8396,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:154</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -8386,7 +8414,7 @@
       <c r="G40" s="2" t="n"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:154</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8424,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:155</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -8414,7 +8442,7 @@
       <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:155</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8452,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:160</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -8442,7 +8470,7 @@
       <c r="G42" s="2" t="n"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:160</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -8452,7 +8480,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html</t>
+          <t>public/embeds/gocus/icon/index.html:161</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -8470,7 +8498,7 @@
       <c r="G43" s="2" t="n"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/icon/index.html:161</t>
+          <t>public/embeds/gocus/icon/index.html</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8508,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:64</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -8498,7 +8526,7 @@
       <c r="G44" s="2" t="n"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:64</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -8508,7 +8536,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:66</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -8526,7 +8554,7 @@
       <c r="G45" s="2" t="n"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:66</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -8536,7 +8564,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:66</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -8554,7 +8582,7 @@
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:66</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8592,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:66</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -8582,7 +8610,7 @@
       <c r="G47" s="2" t="n"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:66</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -8592,7 +8620,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:66</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -8610,7 +8638,7 @@
       <c r="G48" s="2" t="n"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:66</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -8620,7 +8648,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:66</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -8638,7 +8666,7 @@
       <c r="G49" s="2" t="n"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:66</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -8648,7 +8676,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:66</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -8666,7 +8694,7 @@
       <c r="G50" s="2" t="n"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:66</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8704,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:66</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -8694,7 +8722,7 @@
       <c r="G51" s="2" t="n"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:66</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8732,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:66</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -8722,7 +8750,7 @@
       <c r="G52" s="2" t="n"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:66</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8760,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:66</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -8750,7 +8778,7 @@
       <c r="G53" s="2" t="n"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:66</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -8760,7 +8788,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:66</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -8778,7 +8806,7 @@
       <c r="G54" s="2" t="n"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:66</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8816,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:66</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -8806,7 +8834,7 @@
       <c r="G55" s="2" t="n"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:66</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -8816,7 +8844,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:66</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -8834,7 +8862,7 @@
       <c r="G56" s="2" t="n"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:66</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8872,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:66</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -8862,7 +8890,7 @@
       <c r="G57" s="2" t="n"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:66</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8900,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:66</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -8890,7 +8918,7 @@
       <c r="G58" s="2" t="n"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:66</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8928,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:66</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -8918,7 +8946,7 @@
       <c r="G59" s="2" t="n"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:66</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -8928,7 +8956,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:66</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -8946,7 +8974,7 @@
       <c r="G60" s="2" t="n"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:66</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -8956,7 +8984,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:66</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -8974,7 +9002,7 @@
       <c r="G61" s="2" t="n"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:66</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -8984,7 +9012,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:66</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -9002,7 +9030,7 @@
       <c r="G62" s="2" t="n"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:66</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -9012,7 +9040,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:67</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -9030,7 +9058,7 @@
       <c r="G63" s="2" t="n"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:67</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -9040,7 +9068,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:67</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -9058,7 +9086,7 @@
       <c r="G64" s="2" t="n"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:67</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9096,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:67</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -9086,7 +9114,7 @@
       <c r="G65" s="2" t="n"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:67</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9124,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:67</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -9114,7 +9142,7 @@
       <c r="G66" s="2" t="n"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:67</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9152,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:67</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -9142,7 +9170,7 @@
       <c r="G67" s="2" t="n"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:67</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -9152,7 +9180,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:67</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -9170,7 +9198,7 @@
       <c r="G68" s="2" t="n"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:67</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -9180,7 +9208,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:67</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -9198,7 +9226,7 @@
       <c r="G69" s="2" t="n"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:67</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9236,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:67</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -9226,7 +9254,7 @@
       <c r="G70" s="2" t="n"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:67</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9264,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:67</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -9254,7 +9282,7 @@
       <c r="G71" s="2" t="n"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:67</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -9264,7 +9292,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:67</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -9282,7 +9310,7 @@
       <c r="G72" s="2" t="n"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:67</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -9292,7 +9320,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:67</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -9310,7 +9338,7 @@
       <c r="G73" s="2" t="n"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:67</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9348,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:67</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -9338,7 +9366,7 @@
       <c r="G74" s="2" t="n"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:67</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -9348,7 +9376,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:68</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -9366,7 +9394,7 @@
       <c r="G75" s="2" t="n"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:68</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9404,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:68</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -9394,7 +9422,7 @@
       <c r="G76" s="2" t="n"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:68</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -9404,7 +9432,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:69</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -9422,7 +9450,7 @@
       <c r="G77" s="2" t="n"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:69</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -9432,7 +9460,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:69</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -9450,7 +9478,7 @@
       <c r="G78" s="2" t="n"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:69</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9488,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:70</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -9478,7 +9506,7 @@
       <c r="G79" s="2" t="n"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:70</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -9488,7 +9516,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html</t>
+          <t>public/embeds/gocus/panel/guidelines.html:70</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -9506,7 +9534,7 @@
       <c r="G80" s="2" t="n"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/guidelines.html:70</t>
+          <t>public/embeds/gocus/panel/guidelines.html</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9544,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:64</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -9534,7 +9562,7 @@
       <c r="G81" s="2" t="n"/>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:64</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9572,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:66</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -9562,7 +9590,7 @@
       <c r="G82" s="2" t="n"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:66</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -9572,7 +9600,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:66</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -9590,7 +9618,7 @@
       <c r="G83" s="2" t="n"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:66</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -9600,7 +9628,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:66</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -9618,7 +9646,7 @@
       <c r="G84" s="2" t="n"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:66</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -9628,7 +9656,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:66</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -9646,7 +9674,7 @@
       <c r="G85" s="2" t="n"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:66</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -9656,7 +9684,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:66</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -9674,7 +9702,7 @@
       <c r="G86" s="2" t="n"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:66</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9712,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:66</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -9702,7 +9730,7 @@
       <c r="G87" s="2" t="n"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:66</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -9712,7 +9740,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:66</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -9730,7 +9758,7 @@
       <c r="G88" s="2" t="n"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:66</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -9740,7 +9768,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:67</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -9758,7 +9786,7 @@
       <c r="G89" s="2" t="n"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:67</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9796,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:67</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -9786,7 +9814,7 @@
       <c r="G90" s="2" t="n"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:67</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9824,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:68</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -9814,7 +9842,7 @@
       <c r="G91" s="2" t="n"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:68</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9852,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:68</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -9842,7 +9870,7 @@
       <c r="G92" s="2" t="n"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:68</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -9852,7 +9880,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:68</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -9870,7 +9898,7 @@
       <c r="G93" s="2" t="n"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:68</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -9880,7 +9908,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:69</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -9898,7 +9926,7 @@
       <c r="G94" s="2" t="n"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:69</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -9908,7 +9936,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:70</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -9926,7 +9954,7 @@
       <c r="G95" s="2" t="n"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:70</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -9936,7 +9964,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:70</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -9954,7 +9982,7 @@
       <c r="G96" s="2" t="n"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:70</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9992,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:70</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -9982,7 +10010,7 @@
       <c r="G97" s="2" t="n"/>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:70</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -9992,7 +10020,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:70</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -10010,7 +10038,7 @@
       <c r="G98" s="2" t="n"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:70</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10020,7 +10048,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:71</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -10038,7 +10066,7 @@
       <c r="G99" s="2" t="n"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:71</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10048,7 +10076,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:71</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -10066,7 +10094,7 @@
       <c r="G100" s="2" t="n"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:71</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10076,7 +10104,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:72</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -10094,7 +10122,7 @@
       <c r="G101" s="2" t="n"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:72</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10132,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:73</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -10122,7 +10150,7 @@
       <c r="G102" s="2" t="n"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:73</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10132,7 +10160,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:73</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -10150,7 +10178,7 @@
       <c r="G103" s="2" t="n"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:73</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10160,7 +10188,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:73</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -10178,7 +10206,7 @@
       <c r="G104" s="2" t="n"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:73</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10188,7 +10216,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:73</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -10206,7 +10234,7 @@
       <c r="G105" s="2" t="n"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:73</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10216,7 +10244,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:74</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -10234,7 +10262,7 @@
       <c r="G106" s="2" t="n"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:74</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10244,7 +10272,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:75</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -10262,7 +10290,7 @@
       <c r="G107" s="2" t="n"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:75</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10300,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:75</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -10290,7 +10318,7 @@
       <c r="G108" s="2" t="n"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:75</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10300,7 +10328,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:76</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -10318,7 +10346,7 @@
       <c r="G109" s="2" t="n"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:76</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10328,7 +10356,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:76</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -10346,7 +10374,7 @@
       <c r="G110" s="2" t="n"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:76</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10356,7 +10384,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:77</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -10374,7 +10402,7 @@
       <c r="G111" s="2" t="n"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:77</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10384,7 +10412,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:78</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -10402,7 +10430,7 @@
       <c r="G112" s="2" t="n"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:78</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10412,7 +10440,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:78</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -10430,7 +10458,7 @@
       <c r="G113" s="2" t="n"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:78</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10468,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:78</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -10458,7 +10486,7 @@
       <c r="G114" s="2" t="n"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:78</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10496,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:79</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -10486,7 +10514,7 @@
       <c r="G115" s="2" t="n"/>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:79</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10496,7 +10524,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:80</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -10514,7 +10542,7 @@
       <c r="G116" s="2" t="n"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:80</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10524,7 +10552,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:81</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -10542,7 +10570,7 @@
       <c r="G117" s="2" t="n"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:81</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10552,7 +10580,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html</t>
+          <t>public/embeds/gocus/panel/library.html:82</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -10570,7 +10598,7 @@
       <c r="G118" s="2" t="n"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/gocus/panel/library.html:82</t>
+          <t>public/embeds/gocus/panel/library.html</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10608,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:46</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -10598,7 +10626,7 @@
       <c r="G119" s="2" t="n"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:46</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -10608,7 +10636,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:60</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -10626,7 +10654,7 @@
       <c r="G120" s="2" t="n"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:60</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -10636,7 +10664,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:62</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -10654,7 +10682,7 @@
       <c r="G121" s="2" t="n"/>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:62</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -10664,7 +10692,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:63</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -10682,7 +10710,7 @@
       <c r="G122" s="2" t="n"/>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:63</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10720,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:63</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -10710,7 +10738,7 @@
       <c r="G123" s="2" t="n"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:63</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10748,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:64</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -10738,7 +10766,7 @@
       <c r="G124" s="2" t="n"/>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:64</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -10748,7 +10776,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:66</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -10766,7 +10794,7 @@
       <c r="G125" s="2" t="n"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:66</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -10776,7 +10804,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:66</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -10794,7 +10822,7 @@
       <c r="G126" s="2" t="n"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:66</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10832,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:67</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10822,7 +10850,7 @@
       <c r="G127" s="2" t="n"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:67</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -10832,7 +10860,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:67</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10850,7 +10878,7 @@
       <c r="G128" s="2" t="n"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:67</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10888,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:68</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10878,7 +10906,7 @@
       <c r="G129" s="2" t="n"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:68</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -10888,7 +10916,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:70</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10906,7 +10934,7 @@
       <c r="G130" s="2" t="n"/>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:70</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -10916,7 +10944,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:71</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10934,7 +10962,7 @@
       <c r="G131" s="2" t="n"/>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:71</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -10944,7 +10972,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:71</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10962,7 +10990,7 @@
       <c r="G132" s="2" t="n"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:71</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -10972,7 +11000,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:72</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10990,7 +11018,7 @@
       <c r="G133" s="2" t="n"/>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:72</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -11000,7 +11028,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:74</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -11018,7 +11046,7 @@
       <c r="G134" s="2" t="n"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:74</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11056,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:74</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -11046,7 +11074,7 @@
       <c r="G135" s="2" t="n"/>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:74</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11084,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:75</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -11074,7 +11102,7 @@
       <c r="G136" s="2" t="n"/>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:75</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -11084,7 +11112,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:75</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -11102,7 +11130,7 @@
       <c r="G137" s="2" t="n"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:75</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -11112,7 +11140,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:98</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -11130,7 +11158,7 @@
       <c r="G138" s="2" t="n"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:98</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -11140,7 +11168,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:99</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -11158,7 +11186,7 @@
       <c r="G139" s="2" t="n"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:99</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -11168,7 +11196,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:118</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -11186,7 +11214,7 @@
       <c r="G140" s="2" t="n"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:118</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -11196,7 +11224,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:118</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11214,7 +11242,7 @@
       <c r="G141" s="2" t="n"/>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:118</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -11224,7 +11252,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html</t>
+          <t>public/embeds/shokz/wifi/index.html:120</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11242,7 +11270,7 @@
       <c r="G142" s="2" t="n"/>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/shokz/wifi/index.html:120</t>
+          <t>public/embeds/shokz/wifi/index.html</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11280,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:39</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11270,7 +11298,7 @@
       <c r="G143" s="2" t="n"/>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:39</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11308,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:40</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11298,7 +11326,7 @@
       <c r="G144" s="2" t="n"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:40</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11308,7 +11336,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:40</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11326,7 +11354,7 @@
       <c r="G145" s="2" t="n"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:40</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11364,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:42</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11354,7 +11382,7 @@
       <c r="G146" s="2" t="n"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:42</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11392,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:55</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11382,7 +11410,7 @@
       <c r="G147" s="2" t="n"/>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:55</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11392,7 +11420,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:55</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11410,7 +11438,7 @@
       <c r="G148" s="2" t="n"/>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:55</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11420,7 +11448,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:55</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11438,7 +11466,7 @@
       <c r="G149" s="2" t="n"/>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:55</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11476,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:55</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11466,7 +11494,7 @@
       <c r="G150" s="2" t="n"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:55</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11504,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:55</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11494,7 +11522,7 @@
       <c r="G151" s="2" t="n"/>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:55</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11532,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:55</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11522,7 +11550,7 @@
       <c r="G152" s="2" t="n"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:55</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11532,7 +11560,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:55</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11550,7 +11578,7 @@
       <c r="G153" s="2" t="n"/>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:55</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11560,7 +11588,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:55</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11578,7 +11606,7 @@
       <c r="G154" s="2" t="n"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:55</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11588,7 +11616,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:56</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -11606,7 +11634,7 @@
       <c r="G155" s="2" t="n"/>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:56</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11644,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:95</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -11634,7 +11662,7 @@
       <c r="G156" s="2" t="n"/>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:95</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11672,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:101</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -11662,7 +11690,7 @@
       <c r="G157" s="2" t="n"/>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:101</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11672,7 +11700,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:102</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -11690,7 +11718,7 @@
       <c r="G158" s="2" t="n"/>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:102</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11700,7 +11728,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:120</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -11718,7 +11746,7 @@
       <c r="G159" s="2" t="n"/>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:120</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11728,7 +11756,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:129</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -11746,7 +11774,7 @@
       <c r="G160" s="2" t="n"/>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:129</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11784,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:130</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -11774,7 +11802,7 @@
       <c r="G161" s="2" t="n"/>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:130</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11812,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:131</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -11802,7 +11830,7 @@
       <c r="G162" s="2" t="n"/>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:131</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11812,7 +11840,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:153</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -11830,7 +11858,7 @@
       <c r="G163" s="2" t="n"/>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:153</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11840,7 +11868,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:154</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -11858,7 +11886,7 @@
       <c r="G164" s="2" t="n"/>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:154</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11868,7 +11896,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:167</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -11886,7 +11914,7 @@
       <c r="G165" s="2" t="n"/>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:167</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11896,7 +11924,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:167</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -11914,7 +11942,7 @@
       <c r="G166" s="2" t="n"/>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:167</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11924,7 +11952,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:167</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -11942,7 +11970,7 @@
       <c r="G167" s="2" t="n"/>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:167</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11952,7 +11980,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:167</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -11970,7 +11998,7 @@
       <c r="G168" s="2" t="n"/>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:167</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -11980,7 +12008,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:167</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -11998,7 +12026,7 @@
       <c r="G169" s="2" t="n"/>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:167</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -12008,7 +12036,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:168</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -12026,7 +12054,7 @@
       <c r="G170" s="2" t="n"/>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:168</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12064,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:174</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -12054,7 +12082,7 @@
       <c r="G171" s="2" t="n"/>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:174</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -12064,7 +12092,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:180</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -12082,7 +12110,7 @@
       <c r="G172" s="2" t="n"/>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:180</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -12092,7 +12120,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:180</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -12110,7 +12138,7 @@
       <c r="G173" s="2" t="n"/>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:180</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -12120,7 +12148,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:181</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -12138,7 +12166,7 @@
       <c r="G174" s="2" t="n"/>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:181</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -12148,7 +12176,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:190</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -12166,7 +12194,7 @@
       <c r="G175" s="2" t="n"/>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:190</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -12176,7 +12204,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:191</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -12194,7 +12222,7 @@
       <c r="G176" s="2" t="n"/>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:191</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12232,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:204</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -12222,7 +12250,7 @@
       <c r="G177" s="2" t="n"/>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:204</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -12232,7 +12260,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html</t>
+          <t>public/embeds/webstyle/library.html:242</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -12250,7 +12278,7 @@
       <c r="G178" s="2" t="n"/>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>public/embeds/webstyle/library.html:242</t>
+          <t>public/embeds/webstyle/library.html</t>
         </is>
       </c>
     </row>
@@ -12265,7 +12293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13166,17 +13194,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ui.sideProject</t>
+          <t>ui.canvasView</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>小尝试</t>
+          <t>画布</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Side project</t>
+          <t>Canvas</t>
         </is>
       </c>
       <c r="E32" s="2" t="n"/>
@@ -13194,17 +13222,17 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ui.contributions</t>
+          <t>ui.listView</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>过去一年</t>
+          <t>列表</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>in the last year</t>
+          <t>List</t>
         </is>
       </c>
       <c r="E33" s="2" t="n"/>
@@ -13222,17 +13250,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ui.contributionUnit</t>
+          <t>ui.sideProjects</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>次贡献</t>
+          <t>{n} 个小尝试</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>contributions</t>
+          <t>{n} side projects</t>
         </is>
       </c>
       <c r="E34" s="2" t="n"/>
@@ -13250,17 +13278,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ui.less</t>
+          <t>ui.contributions</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>少</t>
+          <t>过去一年</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Less</t>
+          <t>in the last year</t>
         </is>
       </c>
       <c r="E35" s="2" t="n"/>
@@ -13278,17 +13306,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ui.more</t>
+          <t>ui.contributionUnit</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>多</t>
+          <t>次贡献</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>More</t>
+          <t>contributions</t>
         </is>
       </c>
       <c r="E36" s="2" t="n"/>
@@ -13306,17 +13334,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ui.siteTitle</t>
+          <t>ui.less</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>设计作品集</t>
+          <t>少</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Design portfolio</t>
+          <t>Less</t>
         </is>
       </c>
       <c r="E37" s="2" t="n"/>
@@ -13334,17 +13362,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ui.skip</t>
+          <t>ui.more</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>跳至内容</t>
+          <t>多</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Skip to content</t>
+          <t>More</t>
         </is>
       </c>
       <c r="E38" s="2" t="n"/>
@@ -13362,17 +13390,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ui.home</t>
+          <t>ui.siteTitle</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>陆俊荣 — 首页</t>
+          <t>设计作品集</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Jarvis Luk — home</t>
+          <t>Design portfolio</t>
         </is>
       </c>
       <c r="E39" s="2" t="n"/>
@@ -13390,17 +13418,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ui.mainNav</t>
+          <t>ui.skip</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>主导航</t>
+          <t>跳至内容</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Main navigation</t>
+          <t>Skip to content</t>
         </is>
       </c>
       <c r="E40" s="2" t="n"/>
@@ -13418,17 +13446,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>ui.switchLang</t>
+          <t>ui.home</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Switch to English</t>
+          <t>陆俊荣 — 首页</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>切换至中文</t>
+          <t>Jarvis Luk — home</t>
         </is>
       </c>
       <c r="E41" s="2" t="n"/>
@@ -13446,17 +13474,17 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>ui.langShort</t>
+          <t>ui.mainNav</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>主导航</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>Main navigation</t>
         </is>
       </c>
       <c r="E42" s="2" t="n"/>
@@ -13474,17 +13502,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>ui.heroLabel</t>
+          <t>ui.switchLang</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>介绍</t>
+          <t>Switch to English</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>切换至中文</t>
         </is>
       </c>
       <c r="E43" s="2" t="n"/>
@@ -13502,17 +13530,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>ui.heroLines.0</t>
+          <t>ui.langShort</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>以设计，</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Design for</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E44" s="2" t="n"/>
@@ -13530,17 +13558,17 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>ui.heroLines.1</t>
+          <t>ui.heroLabel</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>探索多一点</t>
+          <t>介绍</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>a little more</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="E45" s="2" t="n"/>
@@ -13558,17 +13586,17 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ui.heroLines.2</t>
+          <t>ui.heroLines.0</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>可能。</t>
+          <t>以设计，</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>possibility.</t>
+          <t>Design for</t>
         </is>
       </c>
       <c r="E46" s="2" t="n"/>
@@ -13586,17 +13614,17 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ui.filter</t>
+          <t>ui.heroLines.1</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>筛选项目</t>
+          <t>探索多一点</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Filter projects</t>
+          <t>a little more</t>
         </is>
       </c>
       <c r="E47" s="2" t="n"/>
@@ -13614,17 +13642,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ui.showing</t>
+          <t>ui.heroLines.2</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>正在展示 {n} 个项目</t>
+          <t>可能。</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Showing {n} projects</t>
+          <t>possibility.</t>
         </is>
       </c>
       <c r="E48" s="2" t="n"/>
@@ -13642,17 +13670,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>ui.contributionDay</t>
+          <t>ui.switchView</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>{date} · {n} 次贡献</t>
+          <t>切换视图</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>{n} contributions on {date}</t>
+          <t>Switch view</t>
         </is>
       </c>
       <c r="E49" s="2" t="n"/>
@@ -13670,17 +13698,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>ui.contributionDayOne</t>
+          <t>ui.filter</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>{date} · {n} 次贡献</t>
+          <t>筛选项目</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>{n} contribution on {date}</t>
+          <t>Filter projects</t>
         </is>
       </c>
       <c r="E50" s="2" t="n"/>
@@ -13698,17 +13726,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>ui.months.0</t>
+          <t>ui.showing</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>1月</t>
+          <t>正在展示 {n} 个项目</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Showing {n} projects</t>
         </is>
       </c>
       <c r="E51" s="2" t="n"/>
@@ -13726,17 +13754,17 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>ui.months.1</t>
+          <t>ui.contributionDay</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>2月</t>
+          <t>{date} · {n} 次贡献</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>{n} contributions on {date}</t>
         </is>
       </c>
       <c r="E52" s="2" t="n"/>
@@ -13754,17 +13782,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>ui.months.2</t>
+          <t>ui.contributionDayOne</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>3月</t>
+          <t>{date} · {n} 次贡献</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>{n} contribution on {date}</t>
         </is>
       </c>
       <c r="E53" s="2" t="n"/>
@@ -13782,17 +13810,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>ui.months.3</t>
+          <t>ui.months.0</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>4月</t>
+          <t>1月</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="E54" s="2" t="n"/>
@@ -13810,17 +13838,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>ui.months.4</t>
+          <t>ui.months.1</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>5月</t>
+          <t>2月</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="E55" s="2" t="n"/>
@@ -13838,17 +13866,17 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>ui.months.5</t>
+          <t>ui.months.2</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>6月</t>
+          <t>3月</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="E56" s="2" t="n"/>
@@ -13866,17 +13894,17 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>ui.months.6</t>
+          <t>ui.months.3</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>7月</t>
+          <t>4月</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="E57" s="2" t="n"/>
@@ -13894,17 +13922,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>ui.months.7</t>
+          <t>ui.months.4</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>5月</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>May</t>
         </is>
       </c>
       <c r="E58" s="2" t="n"/>
@@ -13922,17 +13950,17 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>ui.months.8</t>
+          <t>ui.months.5</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>9月</t>
+          <t>6月</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="E59" s="2" t="n"/>
@@ -13950,17 +13978,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>ui.months.9</t>
+          <t>ui.months.6</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>10月</t>
+          <t>7月</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Jul</t>
         </is>
       </c>
       <c r="E60" s="2" t="n"/>
@@ -13978,17 +14006,17 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>ui.months.10</t>
+          <t>ui.months.7</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>11月</t>
+          <t>8月</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="E61" s="2" t="n"/>
@@ -14006,17 +14034,17 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>ui.months.11</t>
+          <t>ui.months.8</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>12月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="E62" s="2" t="n"/>
@@ -14034,17 +14062,17 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>ui.enlarge</t>
+          <t>ui.months.9</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>放大：{caption}</t>
+          <t>10月</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Enlarge: {caption}</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="E63" s="2" t="n"/>
@@ -14062,17 +14090,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>ui.fitScreen</t>
+          <t>ui.months.10</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>适合屏幕</t>
+          <t>11月</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Fit to screen</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="E64" s="2" t="n"/>
@@ -14090,17 +14118,17 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>ui.zoomIn</t>
+          <t>ui.months.11</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>放大细节</t>
+          <t>12月</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Zoom in</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="E65" s="2" t="n"/>
@@ -14118,17 +14146,17 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>ui.prevImage</t>
+          <t>ui.enlarge</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>上一张</t>
+          <t>放大：{caption}</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Previous</t>
+          <t>Enlarge: {caption}</t>
         </is>
       </c>
       <c r="E66" s="2" t="n"/>
@@ -14146,17 +14174,17 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>ui.nextImage</t>
+          <t>ui.fitScreen</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>下一张</t>
+          <t>适合屏幕</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Fit to screen</t>
         </is>
       </c>
       <c r="E67" s="2" t="n"/>
@@ -14174,17 +14202,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>ui.arrowHint</t>
+          <t>ui.zoomIn</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>使用左右方向键浏览</t>
+          <t>放大细节</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Use arrow keys to browse</t>
+          <t>Zoom in</t>
         </is>
       </c>
       <c r="E68" s="2" t="n"/>
@@ -14202,17 +14230,17 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>ui.noVideo</t>
+          <t>ui.prevImage</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>浏览器不支持视频播放</t>
+          <t>上一张</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Your browser does not support video playback.</t>
+          <t>Previous</t>
         </is>
       </c>
       <c r="E69" s="2" t="n"/>
@@ -14230,17 +14258,17 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>ui.references</t>
+          <t>ui.nextImage</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>研究资料与早期探索</t>
+          <t>下一张</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Research material &amp; early explorations</t>
+          <t>Next</t>
         </is>
       </c>
       <c r="E70" s="2" t="n"/>
@@ -14258,17 +14286,17 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>ui.chapters</t>
+          <t>ui.arrowHint</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>项目章节</t>
+          <t>使用左右方向键浏览</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Project chapters</t>
+          <t>Use arrow keys to browse</t>
         </is>
       </c>
       <c r="E71" s="2" t="n"/>
@@ -14286,17 +14314,17 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.canvas</t>
+          <t>ui.noVideo</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>示例页</t>
+          <t>浏览器不支持视频播放</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Canvas</t>
+          <t>Your browser does not support video playback.</t>
         </is>
       </c>
       <c r="E72" s="2" t="n"/>
@@ -14314,17 +14342,17 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.studio</t>
+          <t>ui.references</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>工作台</t>
+          <t>研究资料与早期探索</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Research material &amp; early explorations</t>
         </is>
       </c>
       <c r="E73" s="2" t="n"/>
@@ -14342,17 +14370,17 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.agents</t>
+          <t>ui.chapters</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>项目章节</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Agents</t>
+          <t>Project chapters</t>
         </is>
       </c>
       <c r="E74" s="2" t="n"/>
@@ -14370,17 +14398,17 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.type</t>
+          <t>ui.sectionNav.canvas</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>中文排版</t>
+          <t>示例页</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Chinese type</t>
+          <t>Canvas</t>
         </is>
       </c>
       <c r="E75" s="2" t="n"/>
@@ -14398,17 +14426,17 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.homepage</t>
+          <t>ui.sectionNav.studio</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>首页</t>
+          <t>工作台</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Studio</t>
         </is>
       </c>
       <c r="E76" s="2" t="n"/>
@@ -14426,17 +14454,17 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.training</t>
+          <t>ui.sectionNav.agents</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Agents</t>
         </is>
       </c>
       <c r="E77" s="2" t="n"/>
@@ -14454,17 +14482,17 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.player</t>
+          <t>ui.sectionNav.type</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>播放</t>
+          <t>中文排版</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Chinese type</t>
         </is>
       </c>
       <c r="E78" s="2" t="n"/>
@@ -14482,17 +14510,17 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.data</t>
+          <t>ui.sectionNav.homepage</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>数据</t>
+          <t>首页</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="E79" s="2" t="n"/>
@@ -14510,17 +14538,17 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.import</t>
+          <t>ui.sectionNav.training</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>导入</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="E80" s="2" t="n"/>
@@ -14538,17 +14566,17 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.courses</t>
+          <t>ui.sectionNav.player</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>课程</t>
+          <t>播放</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Courses</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="E81" s="2" t="n"/>
@@ -14566,17 +14594,17 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.tracks</t>
+          <t>ui.sectionNav.data</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>曲库</t>
+          <t>数据</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="E82" s="2" t="n"/>
@@ -14594,17 +14622,17 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.wifi</t>
+          <t>ui.sectionNav.import</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>配网</t>
+          <t>导入</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Wi-Fi</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="E83" s="2" t="n"/>
@@ -14622,17 +14650,17 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.films</t>
+          <t>ui.sectionNav.courses</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>影像</t>
+          <t>课程</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Films</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="E84" s="2" t="n"/>
@@ -14650,17 +14678,17 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.group</t>
+          <t>ui.sectionNav.tracks</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>团体点餐</t>
+          <t>曲库</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Group orders</t>
+          <t>Music</t>
         </is>
       </c>
       <c r="E85" s="2" t="n"/>
@@ -14678,17 +14706,17 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.sound</t>
+          <t>ui.sectionNav.wifi</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>声音</t>
+          <t>配网</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Wi-Fi</t>
         </is>
       </c>
       <c r="E86" s="2" t="n"/>
@@ -14706,17 +14734,17 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.habit</t>
+          <t>ui.sectionNav.films</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>习惯</t>
+          <t>影像</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Habit</t>
+          <t>Films</t>
         </is>
       </c>
       <c r="E87" s="2" t="n"/>
@@ -14734,17 +14762,17 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.mistakes</t>
+          <t>ui.sectionNav.group</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>错题</t>
+          <t>团体点餐</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Mistakes</t>
+          <t>Group orders</t>
         </is>
       </c>
       <c r="E88" s="2" t="n"/>
@@ -14762,17 +14790,17 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.platforms</t>
+          <t>ui.sectionNav.sound</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>多端</t>
+          <t>声音</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Platforms</t>
+          <t>Sound</t>
         </is>
       </c>
       <c r="E89" s="2" t="n"/>
@@ -14790,17 +14818,17 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.build</t>
+          <t>ui.sectionNav.habit</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>开发</t>
+          <t>习惯</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Habit</t>
         </is>
       </c>
       <c r="E90" s="2" t="n"/>
@@ -14818,17 +14846,17 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.graph</t>
+          <t>ui.sectionNav.mistakes</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>提交图</t>
+          <t>错题</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Graph</t>
+          <t>Mistakes</t>
         </is>
       </c>
       <c r="E91" s="2" t="n"/>
@@ -14846,17 +14874,17 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.try</t>
+          <t>ui.sectionNav.platforms</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>试用</t>
+          <t>多端</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Try it</t>
+          <t>Platforms</t>
         </is>
       </c>
       <c r="E92" s="2" t="n"/>
@@ -14874,17 +14902,17 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.library</t>
+          <t>ui.sectionNav.build</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>组件库</t>
+          <t>开发</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Components</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="E93" s="2" t="n"/>
@@ -14902,17 +14930,17 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.guidelines</t>
+          <t>ui.sectionNav.graph</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>设计规范</t>
+          <t>提交图</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Guidelines</t>
+          <t>Graph</t>
         </is>
       </c>
       <c r="E94" s="2" t="n"/>
@@ -14930,17 +14958,17 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.identity</t>
+          <t>ui.sectionNav.try</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>品牌</t>
+          <t>试用</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Try it</t>
         </is>
       </c>
       <c r="E95" s="2" t="n"/>
@@ -14958,17 +14986,17 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.workspace</t>
+          <t>ui.sectionNav.library</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>回到编辑器</t>
+          <t>组件库</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Workspace</t>
+          <t>Components</t>
         </is>
       </c>
       <c r="E96" s="2" t="n"/>
@@ -14986,17 +15014,17 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.actions</t>
+          <t>ui.sectionNav.guidelines</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>操作</t>
+          <t>设计规范</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Guidelines</t>
         </is>
       </c>
       <c r="E97" s="2" t="n"/>
@@ -15014,17 +15042,17 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.research</t>
+          <t>ui.sectionNav.workspace</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>研究</t>
+          <t>回到编辑器</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Workspace</t>
         </is>
       </c>
       <c r="E98" s="2" t="n"/>
@@ -15042,17 +15070,17 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.interaction</t>
+          <t>ui.sectionNav.actions</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>交互</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Interaction</t>
+          <t>Actions</t>
         </is>
       </c>
       <c r="E99" s="2" t="n"/>
@@ -15070,17 +15098,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.prototype</t>
+          <t>ui.sectionNav.research</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>原型</t>
+          <t>研究</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Prototype</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E100" s="2" t="n"/>
@@ -15098,17 +15126,17 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.digital</t>
+          <t>ui.sectionNav.interaction</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>数字体验</t>
+          <t>交互</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Interaction</t>
         </is>
       </c>
       <c r="E101" s="2" t="n"/>
@@ -15126,17 +15154,17 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.testing</t>
+          <t>ui.sectionNav.prototype</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>测试</t>
+          <t>原型</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Prototype</t>
         </is>
       </c>
       <c r="E102" s="2" t="n"/>
@@ -15154,17 +15182,17 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.outcome</t>
+          <t>ui.sectionNav.digital</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>呈现</t>
+          <t>数字体验</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="E103" s="2" t="n"/>
@@ -15182,17 +15210,17 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.context</t>
+          <t>ui.sectionNav.testing</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>情境</t>
+          <t>测试</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Context</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="E104" s="2" t="n"/>
@@ -15210,17 +15238,17 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.community</t>
+          <t>ui.sectionNav.outcome</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>呈现</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="E105" s="2" t="n"/>
@@ -15238,17 +15266,17 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.planning</t>
+          <t>ui.sectionNav.context</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>计划</t>
+          <t>情境</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Planning</t>
+          <t>Context</t>
         </is>
       </c>
       <c r="E106" s="2" t="n"/>
@@ -15266,17 +15294,17 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.ordering</t>
+          <t>ui.sectionNav.identity</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>流程</t>
+          <t>品牌</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Journey</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="E107" s="2" t="n"/>
@@ -15294,17 +15322,17 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.habits</t>
+          <t>ui.sectionNav.community</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>习惯</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Habits</t>
+          <t>Community</t>
         </is>
       </c>
       <c r="E108" s="2" t="n"/>
@@ -15322,17 +15350,17 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.co-design</t>
+          <t>ui.sectionNav.planning</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>共创</t>
+          <t>计划</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Co-design</t>
+          <t>Planning</t>
         </is>
       </c>
       <c r="E109" s="2" t="n"/>
@@ -15350,12 +15378,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.journey</t>
+          <t>ui.sectionNav.ordering</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>旅程</t>
+          <t>流程</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -15378,17 +15406,17 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.assistant</t>
+          <t>ui.sectionNav.habits</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>助手</t>
+          <t>习惯</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Assistant</t>
+          <t>Habits</t>
         </is>
       </c>
       <c r="E111" s="2" t="n"/>
@@ -15406,17 +15434,17 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.system</t>
+          <t>ui.sectionNav.co-design</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>系统</t>
+          <t>共创</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Co-design</t>
         </is>
       </c>
       <c r="E112" s="2" t="n"/>
@@ -15434,17 +15462,17 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.workflow</t>
+          <t>ui.sectionNav.journey</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>需求</t>
+          <t>旅程</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Needs</t>
+          <t>Journey</t>
         </is>
       </c>
       <c r="E113" s="2" t="n"/>
@@ -15462,17 +15490,17 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.space</t>
+          <t>ui.sectionNav.assistant</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>空间</t>
+          <t>助手</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Assistant</t>
         </is>
       </c>
       <c r="E114" s="2" t="n"/>
@@ -15490,17 +15518,17 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.service</t>
+          <t>ui.sectionNav.system</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>服务</t>
+          <t>系统</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>System</t>
         </is>
       </c>
       <c r="E115" s="2" t="n"/>
@@ -15518,17 +15546,17 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.modules</t>
+          <t>ui.sectionNav.workflow</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>模块</t>
+          <t>需求</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Modules</t>
+          <t>Needs</t>
         </is>
       </c>
       <c r="E116" s="2" t="n"/>
@@ -15546,17 +15574,17 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.voices</t>
+          <t>ui.sectionNav.space</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>访谈</t>
+          <t>空间</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Voices</t>
+          <t>Space</t>
         </is>
       </c>
       <c r="E117" s="2" t="n"/>
@@ -15574,17 +15602,17 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.process</t>
+          <t>ui.sectionNav.service</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>流程</t>
+          <t>服务</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="E118" s="2" t="n"/>
@@ -15602,17 +15630,17 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.organize</t>
+          <t>ui.sectionNav.modules</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>工具</t>
+          <t>模块</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Tools</t>
+          <t>Modules</t>
         </is>
       </c>
       <c r="E119" s="2" t="n"/>
@@ -15630,17 +15658,17 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.question</t>
+          <t>ui.sectionNav.voices</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>问题</t>
+          <t>访谈</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>Voices</t>
         </is>
       </c>
       <c r="E120" s="2" t="n"/>
@@ -15658,17 +15686,17 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.structure</t>
+          <t>ui.sectionNav.process</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>结构</t>
+          <t>流程</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Structure</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="E121" s="2" t="n"/>
@@ -15686,17 +15714,17 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.control</t>
+          <t>ui.sectionNav.organize</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>控制</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="E122" s="2" t="n"/>
@@ -15714,17 +15742,17 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.making</t>
+          <t>ui.sectionNav.question</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>制作</t>
+          <t>问题</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Making</t>
+          <t>Question</t>
         </is>
       </c>
       <c r="E123" s="2" t="n"/>
@@ -15742,17 +15770,17 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.experience</t>
+          <t>ui.sectionNav.structure</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>体验</t>
+          <t>结构</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Experience</t>
+          <t>Structure</t>
         </is>
       </c>
       <c r="E124" s="2" t="n"/>
@@ -15770,17 +15798,17 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.daily</t>
+          <t>ui.sectionNav.control</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>日常</t>
+          <t>控制</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="E125" s="2" t="n"/>
@@ -15798,17 +15826,17 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.practice</t>
+          <t>ui.sectionNav.making</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>练习</t>
+          <t>制作</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Practice</t>
+          <t>Making</t>
         </is>
       </c>
       <c r="E126" s="2" t="n"/>
@@ -15826,17 +15854,17 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.reflect</t>
+          <t>ui.sectionNav.experience</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>反馈</t>
+          <t>体验</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Reflect</t>
+          <t>Experience</t>
         </is>
       </c>
       <c r="E127" s="2" t="n"/>
@@ -15854,17 +15882,17 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.platform</t>
+          <t>ui.sectionNav.daily</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>日常</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Daily</t>
         </is>
       </c>
       <c r="E128" s="2" t="n"/>
@@ -15882,17 +15910,17 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.wearable</t>
+          <t>ui.sectionNav.practice</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>穿戴</t>
+          <t>练习</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Wearable</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="E129" s="2" t="n"/>
@@ -15910,17 +15938,17 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.field</t>
+          <t>ui.sectionNav.reflect</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>实测</t>
+          <t>反馈</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Field test</t>
+          <t>Reflect</t>
         </is>
       </c>
       <c r="E130" s="2" t="n"/>
@@ -15938,17 +15966,17 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.station</t>
+          <t>ui.sectionNav.platform</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>站点</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Station</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="E131" s="2" t="n"/>
@@ -15966,17 +15994,17 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>ui.sectionNav.exhibition</t>
+          <t>ui.sectionNav.wearable</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>展陈</t>
+          <t>穿戴</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Exhibition</t>
+          <t>Wearable</t>
         </is>
       </c>
       <c r="E132" s="2" t="n"/>
@@ -15994,17 +16022,17 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>ui.pains</t>
+          <t>ui.sectionNav.field</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>痛点</t>
+          <t>实测</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Pain points</t>
+          <t>Field test</t>
         </is>
       </c>
       <c r="E133" s="2" t="n"/>
@@ -16022,17 +16050,17 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>ui.needs</t>
+          <t>ui.sectionNav.station</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>需求</t>
+          <t>站点</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Needs</t>
+          <t>Station</t>
         </is>
       </c>
       <c r="E134" s="2" t="n"/>
@@ -16050,17 +16078,17 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>ui.workflowHead.0</t>
+          <t>ui.sectionNav.exhibition</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>空间需求</t>
+          <t>展陈</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Exhibition</t>
         </is>
       </c>
       <c r="E135" s="2" t="n"/>
@@ -16078,17 +16106,17 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>ui.workflowHead.1</t>
+          <t>ui.pains</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>工具需求</t>
+          <t>痛点</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Tools</t>
+          <t>Pain points</t>
         </is>
       </c>
       <c r="E136" s="2" t="n"/>
@@ -16106,17 +16134,17 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>ui.workflowHead.2</t>
+          <t>ui.needs</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>需要工坊</t>
+          <t>需求</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Needs</t>
         </is>
       </c>
       <c r="E137" s="2" t="n"/>
@@ -16134,17 +16162,17 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>ui.workflowHead.3</t>
+          <t>ui.workflowHead.0</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>最适合</t>
+          <t>空间需求</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Best place</t>
+          <t>Space</t>
         </is>
       </c>
       <c r="E138" s="2" t="n"/>
@@ -16162,17 +16190,17 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>ui.spaceHead.0</t>
+          <t>ui.workflowHead.1</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>空间</t>
+          <t>工具需求</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="E139" s="2" t="n"/>
@@ -16190,17 +16218,17 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>ui.spaceHead.1</t>
+          <t>ui.workflowHead.2</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>人流</t>
+          <t>需要工坊</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Traffic</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="E140" s="2" t="n"/>
@@ -16218,17 +16246,17 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>ui.suitable</t>
+          <t>ui.workflowHead.3</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>适合部署</t>
+          <t>最适合</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Suitable</t>
+          <t>Best place</t>
         </is>
       </c>
       <c r="E141" s="2" t="n"/>
@@ -16246,17 +16274,17 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>ui.unsuitable</t>
+          <t>ui.spaceHead.0</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>不适合</t>
+          <t>空间</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Not suitable</t>
+          <t>Space</t>
         </is>
       </c>
       <c r="E142" s="2" t="n"/>
@@ -16274,17 +16302,17 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>ui.phase</t>
+          <t>ui.spaceHead.1</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>阶段</t>
+          <t>人流</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Traffic</t>
         </is>
       </c>
       <c r="E143" s="2" t="n"/>
@@ -16302,17 +16330,17 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>ui.bilibili</t>
+          <t>ui.suitable</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>哔哩哔哩</t>
+          <t>适合部署</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>哔哩哔哩</t>
+          <t>Suitable</t>
         </is>
       </c>
       <c r="E144" s="2" t="n"/>
@@ -16330,17 +16358,17 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>ui.playOn</t>
+          <t>ui.unsuitable</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>在{source}播放</t>
+          <t>不适合</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Play on {source}</t>
+          <t>Not suitable</t>
         </is>
       </c>
       <c r="E145" s="2" t="n"/>
@@ -16358,17 +16386,17 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>ui.videoSource</t>
+          <t>ui.phase</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>视频来源</t>
+          <t>阶段</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Video source</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="E146" s="2" t="n"/>
@@ -16386,17 +16414,17 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>ui.openNew</t>
+          <t>ui.bilibili</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>新窗口打开</t>
+          <t>哔哩哔哩</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>哔哩哔哩</t>
         </is>
       </c>
       <c r="E147" s="2" t="n"/>
@@ -16414,17 +16442,17 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>categories.all</t>
+          <t>ui.playOn</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>全部</t>
+          <t>在{source}播放</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Play on {source}</t>
         </is>
       </c>
       <c r="E148" s="2" t="n"/>
@@ -16442,17 +16470,17 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>categories.service</t>
+          <t>ui.videoSource</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>服务与系统</t>
+          <t>视频来源</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Service &amp; systems</t>
+          <t>Video source</t>
         </is>
       </c>
       <c r="E149" s="2" t="n"/>
@@ -16470,17 +16498,17 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>categories.digital</t>
+          <t>ui.openNew</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>数字体验</t>
+          <t>新窗口打开</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Digital experience</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E150" s="2" t="n"/>
@@ -16498,23 +16526,107 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>categories.physical</t>
+          <t>categories.all</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>实体与交互</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Objects &amp; interaction</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E151" s="2" t="n"/>
       <c r="F151" s="2" t="n"/>
       <c r="G151" s="2" t="n"/>
       <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>src/locales/*.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>categories.service</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>服务与系统</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Service &amp; systems</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n"/>
+      <c r="F152" s="2" t="n"/>
+      <c r="G152" s="2" t="n"/>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>src/locales/*.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>categories.digital</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>数字体验</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Digital experience</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n"/>
+      <c r="F153" s="2" t="n"/>
+      <c r="G153" s="2" t="n"/>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>src/locales/*.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>categories.physical</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>实体与交互</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Objects &amp; interaction</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n"/>
+      <c r="F154" s="2" t="n"/>
+      <c r="G154" s="2" t="n"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>src/locales/*.json</t>
         </is>
